--- a/Data Files/Sinistro/CadastroDeRestricao/CadastroRestricao.xlsx
+++ b/Data Files/Sinistro/CadastroDeRestricao/CadastroRestricao.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ\Data Files\Sinistro\CadastroDeRestricao\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Sinistro\CadastroDeRestricao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A8F8F69-1D5D-4FA5-92AB-7F0284440877}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E08FD501-C426-46DA-B94F-F8B267125622}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Status</t>
   </si>
@@ -57,48 +57,6 @@
   </si>
   <si>
     <t>Processar</t>
-  </si>
-  <si>
-    <t>ANÁLISE BLOQUEIO 1737 (TDO)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rodrigo Belisário </t>
-  </si>
-  <si>
-    <t>ANÁLISE BLOQUEIO 1813 (REVALIDAÇÃO DO NÍVEL DE RISCO)</t>
-  </si>
-  <si>
-    <t>12/03/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RMH5D68 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">9882261JCMKD67250 </t>
-  </si>
-  <si>
-    <t>Weldja</t>
-  </si>
-  <si>
-    <t>131621988</t>
-  </si>
-  <si>
-    <t>QPX4B32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93YHSR3J3KJ756508    </t>
-  </si>
-  <si>
-    <t>131248495</t>
-  </si>
-  <si>
-    <t>GGD4J86</t>
-  </si>
-  <si>
-    <t xml:space="preserve">           93YRBB008LJ124111                 </t>
-  </si>
-  <si>
-    <t>131648356</t>
   </si>
 </sst>
 </file>
@@ -279,9 +237,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office 2013 - 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -319,7 +277,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -425,7 +383,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -567,7 +525,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -619,75 +577,17 @@
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>16</v>
-      </c>
       <c r="G2" s="8" t="s">
         <v>8</v>
       </c>
       <c r="H2" s="8"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>8</v>
-      </c>
+      <c r="G3" s="8"/>
       <c r="H3" s="8"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>8</v>
-      </c>
+      <c r="G4" s="8"/>
       <c r="H4" s="8"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -712,31 +612,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
+  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTU0OTU1PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTgvMDUvMjAyMCAyMzo1NzoxMzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxOC8wNS8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
-  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
-</sisl>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97A0AEE1-2848-4A72-BCE5-B9583B575AC3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAB945F2-A4F0-4F66-8E00-009883594EA4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97A0AEE1-2848-4A72-BCE5-B9583B575AC3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Data Files/Sinistro/CadastroDeRestricao/CadastroRestricao.xlsx
+++ b/Data Files/Sinistro/CadastroDeRestricao/CadastroRestricao.xlsx
@@ -1,28 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Sinistro\CadastroDeRestricao\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ\Data Files\Sinistro\CadastroDeRestricao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E08FD501-C426-46DA-B94F-F8B267125622}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr documentId="13_ncr:1_{7284D9DE-9333-4EB6-91C9-9FD3950BD026}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowHeight="11160" windowWidth="20730" xWindow="-120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}" yWindow="-120"/>
   </bookViews>
   <sheets>
-    <sheet name="CadastroDeRestricao" sheetId="3" r:id="rId1"/>
+    <sheet name="CadastroDeRestricao" r:id="rId1" sheetId="3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">CadastroDeRestricao!$A$1:$H$1</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">CadastroDeRestricao!$A$1:$H$1</definedName>
     <definedName name="Base">#REF!</definedName>
     <definedName name="TAB">#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="17">
   <si>
     <t>Status</t>
   </si>
@@ -57,6 +57,30 @@
   </si>
   <si>
     <t>Processar</t>
+  </si>
+  <si>
+    <t>ANÁLISE BLOQUEIO 1813 (REVALIDAÇÃO DO NÍVEL DE RISCO)</t>
+  </si>
+  <si>
+    <t>13/08/2025</t>
+  </si>
+  <si>
+    <t>SDW8C89</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9BD341ACZPY837831                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rodrigo Belisário </t>
+  </si>
+  <si>
+    <t>133902957</t>
+  </si>
+  <si>
+    <t>Processado</t>
+  </si>
+  <si>
+    <t> Ativação realizada</t>
   </si>
 </sst>
 </file>
@@ -178,53 +202,53 @@
     </border>
   </borders>
   <cellStyleXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0" borderId="0" fillId="0" fontId="1" numFmtId="43"/>
+    <xf applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0" borderId="0" fillId="0" fontId="1" numFmtId="164"/>
   </cellStyleXfs>
   <cellXfs count="12">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
+    <xf applyAlignment="1" applyBorder="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="0" numFmtId="49" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" borderId="1" fillId="3" fontId="4" numFmtId="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="3" fontId="5" numFmtId="49" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" borderId="1" fillId="3" fontId="6" numFmtId="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="5" fontId="2" numFmtId="49" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="2" fontId="2" numFmtId="49" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf applyAlignment="1" applyBorder="1" applyFill="1" borderId="1" fillId="4" fontId="0" numFmtId="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="3" numFmtId="49" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf applyAlignment="1" applyBorder="1" borderId="1" fillId="0" fontId="0" numFmtId="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf applyAlignment="1" applyBorder="1" applyFont="1" borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="3" fontId="4" numFmtId="49" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moeda 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Vírgula" xfId="1" builtinId="3"/>
+    <cellStyle builtinId="0" name="Normal" xfId="0"/>
+    <cellStyle builtinId="3" name="Vírgula" xfId="1"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -241,10 +265,10 @@
   <a:themeElements>
     <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr lastClr="000000" val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr lastClr="FFFFFF" val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -279,7 +303,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin panose="020F0302020204030204" typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -331,7 +355,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin panose="020F0502020204030204" typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -442,21 +466,21 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="6350">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="12700">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="19050">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -473,7 +497,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw algn="ctr" blurRad="57150" dir="5400000" dist="19050" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -525,32 +549,32 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" name="Office 2013 - 2022 Theme" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="38" style="1" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="19.5703125" style="9" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="30.140625" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="42.5703125" style="9" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="47.5703125" style="9" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="15.85546875" style="1" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="14.5703125" style="10" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="59.140625" style="9" customWidth="1" collapsed="1"/>
-    <col min="9" max="16384" width="9.140625" style="9" collapsed="1"/>
+    <col min="1" max="1" customWidth="true" style="1" width="38.0" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="9" width="19.5703125" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="30.140625" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="9" width="42.5703125" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="9" width="47.5703125" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="1" width="15.85546875" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="10" width="14.5703125" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="9" width="59.140625" collapsed="true"/>
+    <col min="9" max="16384" style="9" width="9.140625" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row customFormat="1" r="1" s="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>2</v>
       </c>
@@ -577,36 +601,40 @@
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="G2" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="H2" s="8"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
+        <v>15</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>16</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:H1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="7" type="noConversion"/>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageMargins bottom="0.78740157499999996" footer="0.31496062000000002" header="0.31496062000000002" left="0.511811024" right="0.511811024" top="0.78740157499999996"/>
+  <pageSetup horizontalDpi="300" orientation="portrait" paperSize="9" r:id="rId1" verticalDpi="300"/>
   <headerFooter>
-    <oddFooter>&amp;L&amp;"Calibri,Regular"&amp;08&amp;B&amp;K7F7F7FClassificação Allianz:&amp;K595959 &amp;K7F7F7FPÚBLICO</oddFooter>
-    <evenFooter>&amp;L&amp;"Calibri,Regular"&amp;08&amp;B&amp;K7F7F7FClassificação Allianz:&amp;K595959 &amp;K7F7F7FPÚBLICO</evenFooter>
-    <firstFooter>&amp;L&amp;"Calibri,Regular"&amp;08&amp;B&amp;K7F7F7FClassificação Allianz:&amp;K595959 &amp;K7F7F7FPÚBLICO</firstFooter>
+    <oddFooter><![CDATA[&L&"Calibri,Regular"&08&B&K7F7F7FClassificação Allianz:&K595959 &K7F7F7FPÚBLICO]]></oddFooter>
+    <evenFooter><![CDATA[&L&"Calibri,Regular"&08&B&K7F7F7FClassificação Allianz:&K595959 &K7F7F7FPÚBLICO]]></evenFooter>
+    <firstFooter><![CDATA[&L&"Calibri,Regular"&08&B&K7F7F7FClassificação Allianz:&K595959 &K7F7F7FPÚBLICO]]></firstFooter>
   </headerFooter>
 </worksheet>
 </file>

--- a/Data Files/Sinistro/CadastroDeRestricao/CadastroRestricao.xlsx
+++ b/Data Files/Sinistro/CadastroDeRestricao/CadastroRestricao.xlsx
@@ -1,28 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ\Data Files\Sinistro\CadastroDeRestricao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{7284D9DE-9333-4EB6-91C9-9FD3950BD026}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76503CC8-3ACA-45E8-8B85-9F0C9D11F6BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="11160" windowWidth="20730" xWindow="-120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}" yWindow="-120"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="CadastroDeRestricao" r:id="rId1" sheetId="3"/>
+    <sheet name="CadastroDeRestricao" sheetId="3" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">CadastroDeRestricao!$A$1:$H$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">CadastroDeRestricao!$A$1:$H$1</definedName>
     <definedName name="Base">#REF!</definedName>
     <definedName name="TAB">#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>Status</t>
   </si>
@@ -62,25 +62,19 @@
     <t>ANÁLISE BLOQUEIO 1813 (REVALIDAÇÃO DO NÍVEL DE RISCO)</t>
   </si>
   <si>
-    <t>13/08/2025</t>
-  </si>
-  <si>
-    <t>SDW8C89</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9BD341ACZPY837831                   </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rodrigo Belisário </t>
-  </si>
-  <si>
-    <t>133902957</t>
-  </si>
-  <si>
-    <t>Processado</t>
-  </si>
-  <si>
-    <t> Ativação realizada</t>
+    <t>31/01/2026</t>
+  </si>
+  <si>
+    <t>RTR2E82</t>
+  </si>
+  <si>
+    <t>9BD2651PAN9203643</t>
+  </si>
+  <si>
+    <t>Priscila Oliveira</t>
+  </si>
+  <si>
+    <t>136466747</t>
   </si>
 </sst>
 </file>
@@ -91,7 +85,7 @@
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_-&quot;R$&quot;* #,##0.00_-;\-&quot;R$&quot;* #,##0.00_-;_-&quot;R$&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -113,12 +107,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -202,53 +190,50 @@
     </border>
   </borders>
   <cellStyleXfs count="3">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
-    <xf applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0" borderId="0" fillId="0" fontId="1" numFmtId="43"/>
-    <xf applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0" borderId="0" fillId="0" fontId="1" numFmtId="164"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
-    <xf applyAlignment="1" applyBorder="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="0" numFmtId="49" xfId="0">
+  <cellXfs count="11">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" borderId="1" fillId="3" fontId="4" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="3" fontId="5" numFmtId="49" xfId="0">
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" borderId="1" fillId="3" fontId="6" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="5" fontId="2" numFmtId="49" xfId="1">
+    <xf numFmtId="49" fontId="2" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="2" fontId="2" numFmtId="49" xfId="1">
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" borderId="1" fillId="4" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="3" numFmtId="49" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf applyAlignment="1" applyBorder="1" borderId="1" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFont="1" borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="3" fontId="4" numFmtId="49" xfId="0">
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moeda 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
-    <cellStyle builtinId="0" name="Normal" xfId="0"/>
-    <cellStyle builtinId="3" name="Vírgula" xfId="1"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Vírgula" xfId="1" builtinId="3"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -265,10 +250,10 @@
   <a:themeElements>
     <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -303,7 +288,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
-        <a:latin panose="020F0302020204030204" typeface="Calibri Light"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -355,7 +340,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin panose="020F0502020204030204" typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -466,21 +451,21 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="6350">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="12700">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="19050">
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -497,7 +482,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw algn="ctr" blurRad="57150" dir="5400000" dist="19050" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -549,33 +534,33 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" name="Office 2013 - 2022 Theme" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="1" width="38.0" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" style="9" width="19.5703125" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="30.140625" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="9" width="42.5703125" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="9" width="47.5703125" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="1" width="15.85546875" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="10" width="14.5703125" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="9" width="59.140625" collapsed="true"/>
-    <col min="9" max="16384" style="9" width="9.140625" collapsed="true"/>
+    <col min="1" max="1" width="38" style="1" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="19.5546875" style="8" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="30.109375" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="42.5546875" style="8" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="47.5546875" style="8" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="15.88671875" style="1" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="14.5546875" style="9" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="59.109375" style="8" customWidth="1" collapsed="1"/>
+    <col min="9" max="16384" width="9.109375" style="8" collapsed="1"/>
   </cols>
   <sheetData>
-    <row customFormat="1" r="1" s="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="10" t="s">
         <v>2</v>
       </c>
       <c r="B1" s="2" t="s">
@@ -600,41 +585,38 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="8" t="s">
         <v>11</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="8" t="s">
         <v>13</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" s="8" t="s">
-        <v>16</v>
+      <c r="G2" s="9" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:H1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <phoneticPr fontId="7" type="noConversion"/>
-  <pageMargins bottom="0.78740157499999996" footer="0.31496062000000002" header="0.31496062000000002" left="0.511811024" right="0.511811024" top="0.78740157499999996"/>
-  <pageSetup horizontalDpi="300" orientation="portrait" paperSize="9" r:id="rId1" verticalDpi="300"/>
+  <phoneticPr fontId="6" type="noConversion"/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <headerFooter>
-    <oddFooter><![CDATA[&L&"Calibri,Regular"&08&B&K7F7F7FClassificação Allianz:&K595959 &K7F7F7FPÚBLICO]]></oddFooter>
-    <evenFooter><![CDATA[&L&"Calibri,Regular"&08&B&K7F7F7FClassificação Allianz:&K595959 &K7F7F7FPÚBLICO]]></evenFooter>
-    <firstFooter><![CDATA[&L&"Calibri,Regular"&08&B&K7F7F7FClassificação Allianz:&K595959 &K7F7F7FPÚBLICO]]></firstFooter>
+    <oddFooter>&amp;L&amp;"Calibri,Regular"&amp;08&amp;B&amp;K7F7F7FClassificação Allianz:&amp;K595959 &amp;K7F7F7FPÚBLICO</oddFooter>
+    <evenFooter>&amp;L&amp;"Calibri,Regular"&amp;08&amp;B&amp;K7F7F7FClassificação Allianz:&amp;K595959 &amp;K7F7F7FPÚBLICO</evenFooter>
+    <firstFooter>&amp;L&amp;"Calibri,Regular"&amp;08&amp;B&amp;K7F7F7FClassificação Allianz:&amp;K595959 &amp;K7F7F7FPÚBLICO</firstFooter>
   </headerFooter>
 </worksheet>
 </file>

--- a/Data Files/Sinistro/CadastroDeRestricao/CadastroRestricao.xlsx
+++ b/Data Files/Sinistro/CadastroDeRestricao/CadastroRestricao.xlsx
@@ -1,28 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ\Data Files\Sinistro\CadastroDeRestricao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76503CC8-3ACA-45E8-8B85-9F0C9D11F6BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr documentId="13_ncr:1_{2ADB6C69-2A6B-48B5-A0AA-F434F91DB836}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowHeight="11040" windowWidth="20730" xWindow="-120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}" yWindow="-120"/>
   </bookViews>
   <sheets>
-    <sheet name="CadastroDeRestricao" sheetId="3" r:id="rId1"/>
+    <sheet name="CadastroDeRestricao" r:id="rId1" sheetId="3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">CadastroDeRestricao!$A$1:$H$1</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">CadastroDeRestricao!$A$1:$H$1</definedName>
     <definedName name="Base">#REF!</definedName>
     <definedName name="TAB">#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="17">
   <si>
     <t>Status</t>
   </si>
@@ -62,19 +62,25 @@
     <t>ANÁLISE BLOQUEIO 1813 (REVALIDAÇÃO DO NÍVEL DE RISCO)</t>
   </si>
   <si>
-    <t>31/01/2026</t>
-  </si>
-  <si>
-    <t>RTR2E82</t>
-  </si>
-  <si>
-    <t>9BD2651PAN9203643</t>
-  </si>
-  <si>
     <t>Priscila Oliveira</t>
   </si>
   <si>
-    <t>136466747</t>
+    <t>10/07/2026</t>
+  </si>
+  <si>
+    <t>JBX9I09</t>
+  </si>
+  <si>
+    <t>9BGEB69A0PG268384</t>
+  </si>
+  <si>
+    <t>136717581</t>
+  </si>
+  <si>
+    <t>Processado</t>
+  </si>
+  <si>
+    <t> Ativação realizada</t>
   </si>
 </sst>
 </file>
@@ -190,50 +196,50 @@
     </border>
   </borders>
   <cellStyleXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0" borderId="0" fillId="0" fontId="1" numFmtId="43"/>
+    <xf applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0" borderId="0" fillId="0" fontId="1" numFmtId="164"/>
   </cellStyleXfs>
   <cellXfs count="11">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
+    <xf applyAlignment="1" applyBorder="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="0" numFmtId="49" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="3" fontId="4" numFmtId="49" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" borderId="1" fillId="3" fontId="5" numFmtId="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="5" fontId="2" numFmtId="49" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="2" fontId="2" numFmtId="49" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf applyAlignment="1" applyBorder="1" applyFill="1" borderId="1" fillId="4" fontId="0" numFmtId="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf applyAlignment="1" applyBorder="1" borderId="1" fillId="0" fontId="0" numFmtId="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf applyAlignment="1" applyBorder="1" applyFont="1" borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="3" fontId="3" numFmtId="49" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moeda 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Vírgula" xfId="1" builtinId="3"/>
+    <cellStyle builtinId="0" name="Normal" xfId="0"/>
+    <cellStyle builtinId="3" name="Vírgula" xfId="1"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -250,10 +256,10 @@
   <a:themeElements>
     <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr lastClr="000000" val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr lastClr="FFFFFF" val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -288,7 +294,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin panose="020F0302020204030204" typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -340,7 +346,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin panose="020F0502020204030204" typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -451,21 +457,21 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="6350">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="12700">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="19050">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -482,7 +488,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw algn="ctr" blurRad="57150" dir="5400000" dist="19050" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -534,32 +540,32 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" name="Office 2013 - 2022 Theme" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="38" style="1" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="19.5546875" style="8" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="30.109375" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="42.5546875" style="8" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="47.5546875" style="8" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="15.88671875" style="1" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="14.5546875" style="9" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="59.109375" style="8" customWidth="1" collapsed="1"/>
-    <col min="9" max="16384" width="9.109375" style="8" collapsed="1"/>
+    <col min="1" max="1" customWidth="true" style="1" width="38.0" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="8" width="19.5703125" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="30.140625" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="8" width="42.5703125" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="8" width="47.5703125" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="1" width="15.85546875" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="9" width="14.5703125" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="8" width="59.140625" collapsed="true"/>
+    <col min="9" max="16384" style="8" width="9.140625" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row customFormat="1" r="1" s="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
         <v>2</v>
       </c>
@@ -585,38 +591,41 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>9</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>14</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>8</v>
+        <v>15</v>
+      </c>
+      <c r="H2" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:H1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="6" type="noConversion"/>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageMargins bottom="0.78740157499999996" footer="0.31496062000000002" header="0.31496062000000002" left="0.511811024" right="0.511811024" top="0.78740157499999996"/>
+  <pageSetup horizontalDpi="300" orientation="portrait" paperSize="9" r:id="rId1" verticalDpi="300"/>
   <headerFooter>
-    <oddFooter>&amp;L&amp;"Calibri,Regular"&amp;08&amp;B&amp;K7F7F7FClassificação Allianz:&amp;K595959 &amp;K7F7F7FPÚBLICO</oddFooter>
-    <evenFooter>&amp;L&amp;"Calibri,Regular"&amp;08&amp;B&amp;K7F7F7FClassificação Allianz:&amp;K595959 &amp;K7F7F7FPÚBLICO</evenFooter>
-    <firstFooter>&amp;L&amp;"Calibri,Regular"&amp;08&amp;B&amp;K7F7F7FClassificação Allianz:&amp;K595959 &amp;K7F7F7FPÚBLICO</firstFooter>
+    <oddFooter><![CDATA[&L&"Calibri,Regular"&08&B&K7F7F7FClassificação Allianz:&K595959 &K7F7F7FPÚBLICO]]></oddFooter>
+    <evenFooter><![CDATA[&L&"Calibri,Regular"&08&B&K7F7F7FClassificação Allianz:&K595959 &K7F7F7FPÚBLICO]]></evenFooter>
+    <firstFooter><![CDATA[&L&"Calibri,Regular"&08&B&K7F7F7FClassificação Allianz:&K595959 &K7F7F7FPÚBLICO]]></firstFooter>
   </headerFooter>
 </worksheet>
 </file>
